--- a/Result/profitability/8102.xlsx
+++ b/Result/profitability/8102.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM25"/>
+  <dimension ref="A1:AM26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.12</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7337499999999999</v>
+        <v>0.71375</v>
       </c>
       <c r="N2" t="n">
-        <v>41.195</v>
+        <v>41.33750000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.83</v>
       </c>
       <c r="M3" t="n">
-        <v>0.48625</v>
+        <v>0.36625</v>
       </c>
       <c r="N3" t="n">
-        <v>40.61625</v>
+        <v>40.16500000000001</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-1.53</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05125000000000005</v>
+        <v>0.04375000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>38.7625</v>
+        <v>38.82125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,13 +1018,13 @@
         <v>0.01</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.07874999999999996</v>
+        <v>0.04875000000000002</v>
       </c>
       <c r="N5" t="n">
-        <v>38.21375</v>
+        <v>40.1775</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.37</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.12125</v>
+        <v>-0.07374999999999998</v>
       </c>
       <c r="N6" t="n">
-        <v>39.88875</v>
+        <v>41.06</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.2</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1725</v>
+        <v>-0.12625</v>
       </c>
       <c r="N7" t="n">
-        <v>41.45625</v>
+        <v>41.9125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -3603,6 +3603,133 @@
       </c>
       <c r="AM25" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>8102</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>123</v>
+      </c>
+      <c r="D26" t="n">
+        <v>66</v>
+      </c>
+      <c r="E26" t="n">
+        <v>57</v>
+      </c>
+      <c r="F26" t="n">
+        <v>46.27</v>
+      </c>
+      <c r="G26" t="n">
+        <v>26</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>21.36%</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>27</v>
+      </c>
+      <c r="K26" t="n">
+        <v>23</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.8424999999999999</v>
+      </c>
+      <c r="N26" t="n">
+        <v>41.675</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.475</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.2767660044150111</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>-34</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.5140706806282724</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK26" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
